--- a/config/classificacao_receita.xlsx
+++ b/config/classificacao_receita.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PORTABILIDADE</t>
+          <t>PORTADO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -496,10 +496,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PORTABILIDADE PF</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>PORTADO PF</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,7 +516,6 @@
           <t>MIGRACAO DE TECNOLOGIA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -525,9 +523,6 @@
           <t>MIGRAÇÃO DE TECNOLOGIA</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -620,7 +615,6 @@
           <t>All / Fixa Básica PF SVA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>All / Móvel - Aparelho</t>
@@ -638,7 +632,6 @@
           <t>All / Fixa Básica PF - Voz</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>All / Móvel - Acessório</t>
@@ -656,8 +649,6 @@
           <t>All / Fixa Básica SVA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -670,8 +661,6 @@
           <t>All / Fixa Básica - TV</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,8 +673,6 @@
           <t>All / Fixa Básica - Voz</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -698,8 +685,6 @@
           <t>All / Móvel PF - Voz</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -712,8 +697,6 @@
           <t>All / Móvel - Voz</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -721,9 +704,6 @@
           <t>All / Google</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -731,9 +711,6 @@
           <t>All / MDM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -741,9 +718,6 @@
           <t>All / Móvel - Alta Dados</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -751,9 +725,6 @@
           <t>All / Móvel - M2M</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -761,9 +732,6 @@
           <t>All / Móvel - Modem</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -771,9 +739,6 @@
           <t>All / Móvel - Pacote de Dados</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -781,9 +746,6 @@
           <t>All / Móvel - Pacote de SMS</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -791,9 +753,6 @@
           <t>All / Móvel PF - Voz</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -801,9 +760,6 @@
           <t>All / Móvel - SVA</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -811,9 +767,6 @@
           <t>All / Móvel - Voz</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -821,9 +774,6 @@
           <t>All / Office</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -831,9 +781,6 @@
           <t>All / TI</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -841,9 +788,6 @@
           <t>All / Vivo Tech</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -851,9 +795,6 @@
           <t>All / Vivo Travel</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -861,9 +802,6 @@
           <t>All / Vivo Voz Negocio</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
